--- a/file/tracking-list.xlsx
+++ b/file/tracking-list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867877FE-04DB-4C65-85B1-EBA73FC293CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E59110-B0E4-41B4-821C-4141FAC0D38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{127A3AFD-68BF-4CB3-BE69-28EAF96A9C8C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{127A3AFD-68BF-4CB3-BE69-28EAF96A9C8C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="442">
   <si>
     <t>아크로리버하임</t>
   </si>
@@ -1338,6 +1338,42 @@
   </si>
   <si>
     <t>래미안파크스위트</t>
+  </si>
+  <si>
+    <t>영동한양1차</t>
+  </si>
+  <si>
+    <t>청담르엘</t>
+  </si>
+  <si>
+    <t>래미안라클래시</t>
+  </si>
+  <si>
+    <t>래미안대치팰리스</t>
+  </si>
+  <si>
+    <t>도곡렉슬</t>
+  </si>
+  <si>
+    <t>대치르엘</t>
+  </si>
+  <si>
+    <t>개포자이프레지던스</t>
+  </si>
+  <si>
+    <t>디에이치퍼스티어아이파크</t>
+  </si>
+  <si>
+    <t>디에이치자이개포</t>
+  </si>
+  <si>
+    <t>삼익</t>
+  </si>
+  <si>
+    <t>강남자곡아이파크</t>
+  </si>
+  <si>
+    <t>세곡푸르지오</t>
   </si>
 </sst>
 </file>
@@ -1798,7 +1834,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CFC15EF-5188-42DD-AADD-57E027220B54}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B311"/>
+  <dimension ref="A1:B323"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="31.3984375" customWidth="1"/>
@@ -4292,6 +4328,102 @@
         <v>429</v>
       </c>
     </row>
+    <row r="312" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A312" s="9">
+        <v>494</v>
+      </c>
+      <c r="B312" s="11" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A313" s="9">
+        <v>182057</v>
+      </c>
+      <c r="B313" s="14" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A314" s="9">
+        <v>127477</v>
+      </c>
+      <c r="B314" s="11" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A315" s="8">
+        <v>180280</v>
+      </c>
+      <c r="B315" s="14" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A316" s="8">
+        <v>11698</v>
+      </c>
+      <c r="B316" s="14" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A317" s="9">
+        <v>127973</v>
+      </c>
+      <c r="B317" s="11" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A318" s="8">
+        <v>128527</v>
+      </c>
+      <c r="B318" s="14" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A319" s="8">
+        <v>134062</v>
+      </c>
+      <c r="B319" s="14" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A320" s="8">
+        <v>121971</v>
+      </c>
+      <c r="B320" s="14" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A321" s="8">
+        <v>668</v>
+      </c>
+      <c r="B321" s="14" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A322" s="9">
+        <v>113680</v>
+      </c>
+      <c r="B322" s="11" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A323" s="9">
+        <v>103578</v>
+      </c>
+      <c r="B323" s="11" t="s">
+        <v>441</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
